--- a/sheets/민요/검수/희망가.xlsx
+++ b/sheets/민요/검수/희망가.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,33 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4018,8 +4125,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4038,971 +4149,929 @@
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">희망가 — 민요채보-2/희망가.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">희망가</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">곰</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">푸</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">희</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="P3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="C4" s="14"/>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="14"/>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="G4" s="14"/>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="14"/>
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="K4" s="14"/>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">귀</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="O4" s="14"/>
+      <c r="P4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">른</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">망</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="M5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="Q5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">생</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">희</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="Q6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">족</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">영</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">망</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P7" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
+      <c r="Q7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="C8" s="15"/>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">흔</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">히</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">높</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">할</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無
 仲</t>
-        </is>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">히</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="K9" s="13"/>
+      <c r="L9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
+      <c r="N9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="O9" s="13"/>
+      <c r="P9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="Q9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C10" s="14"/>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="E10" s="14"/>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I10" s="14"/>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無
 仲</t>
-        </is>
-      </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="K10" s="14"/>
+      <c r="L10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="M10" s="14"/>
+      <c r="N10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="O10" s="14"/>
+      <c r="P10" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無
 仲</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="Q10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">났</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="15"/>
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="E11" s="15"/>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G11" s="15"/>
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="15"/>
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="K11" s="15"/>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="M11" s="15"/>
+      <c r="N11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O11" s="15"/>
+      <c r="P11" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="Q11" s="15"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="C12" s="13"/>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">솟</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="K12" s="13"/>
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 仲</t>
         </is>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
+      <c r="O12" s="13"/>
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="Q12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="14"/>
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="E13" s="14"/>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="G13" s="14"/>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="K13" s="14"/>
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M13" s="14"/>
+      <c r="N13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="O13" s="14"/>
+      <c r="P13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="Q13" s="14"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">⁚</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="15"/>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="K14" s="15"/>
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">면</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="O14" s="15"/>
+      <c r="P14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:Q2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/희망가.xlsx
+++ b/sheets/민요/검수/희망가.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/희망가.xlsx
+++ b/sheets/민요/검수/희망가.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4152,101 +4193,101 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">희망가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">빛</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">빛</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
       </c>
-      <c r="N3" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
       </c>
-      <c r="P3" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="Q3" s="11" t="inlineStr">
+      <c r="P3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="Q3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4254,74 +4295,74 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">할</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">족</t>
         </is>
       </c>
-      <c r="L4" s="18" t="inlineStr">
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M4" s="12" t="inlineStr">
+      <c r="M4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
+      <c r="O4" s="25"/>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="Q4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
@@ -4329,83 +4370,83 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 僙</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">큰</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">삽</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="I5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">삽</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="K5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">영</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="M5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">영</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="Q5" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
@@ -4413,83 +4454,83 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 僙</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">쌩</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">희</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -4497,70 +4538,70 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">쌩</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">히</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="K7" s="25"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">망</t>
         </is>
       </c>
-      <c r="P7" s="17" t="inlineStr">
+      <c r="P7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="Q7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
@@ -4568,62 +4609,62 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="C8" s="28"/>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="E8" s="28"/>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="G8" s="28"/>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="I8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="28"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M8" s="10"/>
-      <c r="N8" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="M8" s="28"/>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="O8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="Q8" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -4631,74 +4672,74 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">큰</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="I9" s="22"/>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">겨</t>
         </is>
       </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
@@ -4706,125 +4747,125 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="I10" s="25"/>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="K10" s="25"/>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M10" s="25"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="O10" s="25"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q10" s="9"/>
+      <c r="Q10" s="25"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="E11" s="28"/>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="I11" s="28"/>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="K11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M11" s="10"/>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="M11" s="28"/>
+      <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O11" s="10"/>
-      <c r="P11" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="Q11" s="10" t="inlineStr">
+      <c r="O11" s="28"/>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="Q11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
@@ -4832,172 +4873,172 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I12" s="8"/>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="I12" s="22"/>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="K12" s="22"/>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="O12" s="8"/>
-      <c r="P12" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="Q12" s="8"/>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="O12" s="22"/>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="Q12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="C13" s="25"/>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17" t="inlineStr">
+      <c r="M13" s="25"/>
+      <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17" t="inlineStr">
+      <c r="O13" s="25"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q13" s="9"/>
+      <c r="Q13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="C14" s="28"/>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="E14" s="28"/>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="G14" s="28"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="K14" s="10" t="inlineStr">
+      <c r="I14" s="28"/>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="K14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="M14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">영</t>
         </is>
       </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">僙</t>
+        </is>
+      </c>
+      <c r="O14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">뭉</t>
         </is>
       </c>
-      <c r="P14" s="17" t="inlineStr">
+      <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>

--- a/sheets/민요/검수/희망가.xlsx
+++ b/sheets/민요/검수/희망가.xlsx
@@ -4170,28 +4170,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4293,11 +4293,11 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C4" s="25"/>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="N4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O4" s="25"/>
@@ -4368,7 +4368,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="Q10" s="25"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="28"/>
@@ -4850,13 +4850,13 @@
       </c>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M11" s="28"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O11" s="28"/>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4948,36 +4948,36 @@
       <c r="G13" s="25"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="25"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="25"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M13" s="25"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="O13" s="25"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
       <c r="G14" s="28"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="28"/>

--- a/sheets/민요/검수/희망가.xlsx
+++ b/sheets/민요/검수/희망가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4221,13 +4244,13 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">빛</t>
         </is>
@@ -4237,7 +4260,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">빛</t>
         </is>
@@ -4247,7 +4270,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
@@ -4257,7 +4280,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -4267,7 +4290,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">부</t>
         </is>
@@ -4277,7 +4300,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="O3" s="22" t="inlineStr">
+      <c r="O3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">비</t>
         </is>
@@ -4287,7 +4310,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="Q3" s="24" t="inlineStr">
+      <c r="Q3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4300,13 +4323,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4316,7 +4339,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="G4" s="25" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4326,7 +4349,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">할</t>
         </is>
@@ -4336,7 +4359,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">족</t>
         </is>
@@ -4346,7 +4369,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M4" s="26" t="inlineStr">
+      <c r="M4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">와</t>
         </is>
@@ -4356,13 +4379,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O4" s="25"/>
+      <c r="O4" s="31"/>
       <c r="P4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="Q4" s="25" t="inlineStr">
+      <c r="Q4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">풍</t>
         </is>
@@ -4376,7 +4399,7 @@
 僙</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">각</t>
         </is>
@@ -4386,7 +4409,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E5" s="28" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">큰</t>
         </is>
@@ -4396,7 +4419,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="G5" s="28" t="inlineStr">
+      <c r="G5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">삽</t>
         </is>
@@ -4406,7 +4429,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="I5" s="28" t="inlineStr">
+      <c r="I5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">삽</t>
         </is>
@@ -4416,7 +4439,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K5" s="28" t="inlineStr">
+      <c r="K5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">영</t>
         </is>
@@ -4426,7 +4449,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="M5" s="28" t="inlineStr">
+      <c r="M5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">영</t>
         </is>
@@ -4436,7 +4459,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O5" s="28" t="inlineStr">
+      <c r="O5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
@@ -4446,7 +4469,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="Q5" s="28" t="inlineStr">
+      <c r="Q5" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">진</t>
         </is>
@@ -4460,7 +4483,7 @@
 僙</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -4470,7 +4493,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">쌩</t>
         </is>
@@ -4480,7 +4503,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -4490,7 +4513,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
@@ -4500,7 +4523,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4510,7 +4533,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">화</t>
         </is>
@@ -4520,7 +4543,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">희</t>
         </is>
@@ -4530,7 +4553,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -4543,13 +4566,13 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="C7" s="25"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">쌩</t>
         </is>
@@ -4559,7 +4582,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">히</t>
         </is>
@@ -4569,19 +4592,19 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="I7" s="25"/>
+      <c r="I7" s="31"/>
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K7" s="25"/>
+      <c r="K7" s="31"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">를</t>
         </is>
@@ -4591,7 +4614,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="O7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">망</t>
         </is>
@@ -4601,7 +4624,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q7" s="25" t="inlineStr">
+      <c r="Q7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
@@ -4614,25 +4637,25 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="C8" s="28"/>
+      <c r="C8" s="34"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E8" s="28"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="G8" s="28"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="I8" s="28" t="inlineStr">
+      <c r="I8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4642,19 +4665,19 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K8" s="28"/>
+      <c r="K8" s="34"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M8" s="28"/>
+      <c r="M8" s="34"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="O8" s="28" t="inlineStr">
+      <c r="O8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4664,7 +4687,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q8" s="28" t="inlineStr">
+      <c r="Q8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -4677,13 +4700,13 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">큰</t>
         </is>
@@ -4693,7 +4716,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4703,13 +4726,13 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="I9" s="22"/>
+      <c r="I9" s="29"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
@@ -4719,7 +4742,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">겨</t>
         </is>
@@ -4729,7 +4752,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="O9" s="22" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">구</t>
         </is>
@@ -4739,7 +4762,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q9" s="22" t="inlineStr">
+      <c r="Q9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
@@ -4752,7 +4775,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">종</t>
         </is>
@@ -4762,7 +4785,7 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E10" s="25" t="inlineStr">
+      <c r="E10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -4772,37 +4795,37 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="G10" s="25"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="I10" s="25"/>
+      <c r="I10" s="31"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="K10" s="25"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M10" s="25"/>
+      <c r="M10" s="31"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O10" s="25"/>
+      <c r="O10" s="31"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q10" s="25"/>
+      <c r="Q10" s="31"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -4811,7 +4834,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -4821,13 +4844,13 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E11" s="28"/>
+      <c r="E11" s="34"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="G11" s="28" t="inlineStr">
+      <c r="G11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -4837,13 +4860,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="28"/>
+      <c r="I11" s="34"/>
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="K11" s="28" t="inlineStr">
+      <c r="K11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -4853,19 +4876,19 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M11" s="28"/>
+      <c r="M11" s="34"/>
       <c r="N11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O11" s="28"/>
+      <c r="O11" s="34"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="Q11" s="28" t="inlineStr">
+      <c r="Q11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">의</t>
         </is>
@@ -4878,37 +4901,37 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="29"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="I12" s="22"/>
+      <c r="I12" s="29"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K12" s="22"/>
+      <c r="K12" s="29"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4918,13 +4941,13 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="O12" s="22"/>
+      <c r="O12" s="29"/>
       <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="Q12" s="22"/>
+      <c r="Q12" s="29"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
@@ -4933,49 +4956,49 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="25"/>
+      <c r="M13" s="31"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O13" s="25"/>
+      <c r="O13" s="31"/>
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q13" s="25"/>
+      <c r="Q13" s="31"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -4984,31 +5007,31 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="C14" s="28"/>
+      <c r="C14" s="34"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="E14" s="28"/>
+      <c r="E14" s="34"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="G14" s="28"/>
+      <c r="G14" s="34"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="28"/>
+      <c r="I14" s="34"/>
       <c r="J14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="K14" s="28" t="inlineStr">
+      <c r="K14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
@@ -5018,7 +5041,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="M14" s="28" t="inlineStr">
+      <c r="M14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">영</t>
         </is>
@@ -5028,7 +5051,7 @@
           <t xml:space="preserve">僙</t>
         </is>
       </c>
-      <c r="O14" s="28" t="inlineStr">
+      <c r="O14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">뭉</t>
         </is>
@@ -5038,7 +5061,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q14" s="28" t="inlineStr">
+      <c r="Q14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>

--- a/sheets/민요/검수/희망가.xlsx
+++ b/sheets/민요/검수/희망가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,31 +227,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -365,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
     </row>
@@ -425,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">인쇄 양식(12정간, 굵은 선 3칸마다), 하단 "- 197 -"는 양식 번호. 상단 줄 번호 1~8(오른쪽=1), 좌측 정간 번호 1~12. 각 율명 열 오른쪽 좁은 칸에 손글씨 가사가 있어 정간별로 전사함. 僙=亻黃(배황종) 추정, 썼=姑(중성 고선)로 판독. 손글씨 겹침으로 일부 율명의 변(亻/氵/없음) 구별이 애매함.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 12정간 양식(굵은 선 3칸마다, 하단 - 197 -) → 3/4·12, 오른쪽부터 8줄(제목 옆 '중모리'). 가사는 각 율명 줄 오른쪽 칸. 侑 모양은 㑲(亻南)로 적음. 無·㒇 위 작은 v/∪ 꾸밈은 ^ 로. 짧은 사선 획은 –, 둥근 점은 · 로 구분. 가사 칸의 점 표시는 생략. 한 곡.</t>
         </is>
       </c>
     </row>
@@ -611,26 +588,22 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㑲</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㑲</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">亻黃(배황종)으로 보이는 글자</t>
-        </is>
-      </c>
+      <c r="J2" s="4"/>
       <c r="K2" s="2"/>
     </row>
     <row r="3">
@@ -851,17 +824,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">무</t>
+          <t xml:space="preserve">만</t>
         </is>
       </c>
       <c r="J8" s="4"/>
@@ -890,12 +863,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|無南</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–
+無南</t>
         </is>
       </c>
       <c r="I9" s="2"/>
@@ -925,17 +899,18 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">仲
+姑</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">의</t>
+          <t xml:space="preserve">났</t>
         </is>
       </c>
       <c r="J10" s="4"/>
@@ -972,7 +947,11 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으</t>
+        </is>
+      </c>
       <c r="J11" s="4"/>
       <c r="K11" s="2"/>
     </row>
@@ -1073,17 +1052,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">비</t>
+          <t xml:space="preserve">너</t>
         </is>
       </c>
       <c r="J14" s="4"/>
@@ -1186,12 +1165,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1225,12 +1204,12 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1303,17 +1282,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">구</t>
+          <t xml:space="preserve">무</t>
         </is>
       </c>
       <c r="J20" s="4"/>
@@ -1342,15 +1321,19 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I21" s="2"/>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">엇</t>
+        </is>
+      </c>
       <c r="J21" s="4"/>
       <c r="K21" s="2"/>
     </row>
@@ -1375,18 +1358,26 @@
       <c r="F22" s="2">
         <v>3</v>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="4"/>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㒇^</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㒇^</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亻無 위 작은 ∪ 모양 꾸밈을 ^ 로</t>
+        </is>
+      </c>
       <c r="K22" s="2"/>
     </row>
     <row r="23">
@@ -1412,15 +1403,19 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">㑲</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I23" s="2"/>
+          <t xml:space="preserve">㑲</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">냐</t>
+        </is>
+      </c>
       <c r="J23" s="4"/>
       <c r="K23" s="2"/>
     </row>
@@ -1445,18 +1440,22 @@
       <c r="F24" s="2">
         <v>4</v>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="4"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짧은 사선, –/· 애매</t>
+        </is>
+      </c>
       <c r="K24" s="2"/>
     </row>
     <row r="25">
@@ -1482,19 +1481,15 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">뭉</t>
-        </is>
-      </c>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="I25" s="2"/>
       <c r="J25" s="4"/>
       <c r="K25" s="2"/>
     </row>
@@ -1521,12 +1516,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㑲</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">㑲</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1558,26 +1553,22 @@
       <c r="F27" s="2">
         <v>1</v>
       </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">와</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기와? 불확실</t>
-        </is>
-      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">귀</t>
+        </is>
+      </c>
+      <c r="J27" s="4"/>
       <c r="K27" s="2"/>
     </row>
     <row r="28">
@@ -1613,7 +1604,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">영</t>
+          <t xml:space="preserve">와</t>
         </is>
       </c>
       <c r="J28" s="4"/>
@@ -1652,7 +1643,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">화</t>
+          <t xml:space="preserve">영</t>
         </is>
       </c>
       <c r="J29" s="4"/>
@@ -1681,17 +1672,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">를</t>
+          <t xml:space="preserve">화</t>
         </is>
       </c>
       <c r="J30" s="4"/>
@@ -1728,7 +1719,11 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I31" s="2"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">를</t>
+        </is>
+      </c>
       <c r="J31" s="4"/>
       <c r="K31" s="2"/>
     </row>
@@ -1755,17 +1750,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">겨</t>
+          <t xml:space="preserve">누</t>
         </is>
       </c>
       <c r="J32" s="4"/>
@@ -1794,12 +1789,13 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|無南</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–
+無南</t>
         </is>
       </c>
       <c r="I33" s="2"/>
@@ -1829,15 +1825,20 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I34" s="2"/>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">렸</t>
+        </is>
+      </c>
       <c r="J34" s="4"/>
       <c r="K34" s="2"/>
     </row>
@@ -1864,17 +1865,17 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">으</t>
         </is>
       </c>
       <c r="J35" s="4"/>
@@ -1903,12 +1904,12 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -1938,17 +1939,17 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">영</t>
+          <t xml:space="preserve">면</t>
         </is>
       </c>
       <c r="J37" s="4"/>
@@ -1977,17 +1978,17 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">하</t>
+          <t xml:space="preserve">희</t>
         </is>
       </c>
       <c r="J38" s="4"/>
@@ -2016,17 +2017,17 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">족</t>
+          <t xml:space="preserve">망</t>
         </is>
       </c>
       <c r="J39" s="4"/>
@@ -2055,17 +2056,17 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">영</t>
+          <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="J40" s="4"/>
@@ -2094,17 +2095,17 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">화</t>
+          <t xml:space="preserve">족</t>
         </is>
       </c>
       <c r="J41" s="4"/>
@@ -2131,18 +2132,26 @@
       <c r="F42" s="2">
         <v>2</v>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I42" s="2"/>
-      <c r="J42" s="4"/>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㑲</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㑲</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">족</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 족 반복으로 보임</t>
+        </is>
+      </c>
       <c r="K42" s="2"/>
     </row>
     <row r="43">
@@ -2168,15 +2177,19 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I43" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">할</t>
+        </is>
+      </c>
       <c r="J43" s="4"/>
       <c r="K43" s="2"/>
     </row>
@@ -2213,7 +2226,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">누</t>
+          <t xml:space="preserve">까</t>
         </is>
       </c>
       <c r="J44" s="4"/>
@@ -2242,12 +2255,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I45" s="2"/>
@@ -2275,22 +2288,22 @@
       <c r="F46" s="2">
         <v>3</v>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="J46" s="4"/>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I46" s="3"/>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">짧은 사선, –/· 애매</t>
+        </is>
+      </c>
       <c r="K46" s="2"/>
     </row>
     <row r="47">
@@ -2316,12 +2329,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I47" s="2"/>
@@ -2351,12 +2364,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I48" s="2"/>
@@ -2386,19 +2399,16 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">니</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I49" s="2"/>
       <c r="J49" s="4"/>
       <c r="K49" s="2"/>
     </row>
@@ -2423,22 +2433,26 @@
       <c r="F50" s="2">
         <v>1</v>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">늘</t>
-        </is>
-      </c>
-      <c r="J50" s="4"/>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">푸</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無 위 작은 v 모양 꾸밈을 ^ 로</t>
+        </is>
+      </c>
       <c r="K50" s="2"/>
     </row>
     <row r="51">
@@ -2464,19 +2478,15 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">할</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I51" s="2"/>
       <c r="J51" s="4"/>
       <c r="K51" s="2"/>
     </row>
@@ -2503,17 +2513,17 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">無^</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">無^</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">삽</t>
+          <t xml:space="preserve">른</t>
         </is>
       </c>
       <c r="J52" s="4"/>
@@ -2542,17 +2552,17 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">無^</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">無^</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">들</t>
+          <t xml:space="preserve">하</t>
         </is>
       </c>
       <c r="J53" s="4"/>
@@ -2581,12 +2591,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I54" s="2"/>
@@ -2616,17 +2626,17 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">늘</t>
         </is>
       </c>
       <c r="J55" s="4"/>
@@ -2655,15 +2665,19 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I56" s="2"/>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">밝</t>
+        </is>
+      </c>
       <c r="J56" s="4"/>
       <c r="K56" s="2"/>
     </row>
@@ -2690,12 +2704,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I57" s="2"/>
@@ -2725,15 +2739,19 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I58" s="2"/>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">은</t>
+        </is>
+      </c>
       <c r="J58" s="4"/>
       <c r="K58" s="2"/>
     </row>
@@ -2760,15 +2778,19 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I59" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달</t>
+        </is>
+      </c>
       <c r="J59" s="4"/>
       <c r="K59" s="2"/>
     </row>
@@ -2795,15 +2817,19 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I60" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
       <c r="J60" s="4"/>
       <c r="K60" s="2"/>
     </row>
@@ -2830,15 +2856,19 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I61" s="2"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">래</t>
+        </is>
+      </c>
       <c r="J61" s="4"/>
       <c r="K61" s="2"/>
     </row>
@@ -2865,17 +2895,17 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">빛</t>
+          <t xml:space="preserve">곰</t>
         </is>
       </c>
       <c r="J62" s="4"/>
@@ -2904,19 +2934,15 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I63" s="2"/>
       <c r="J63" s="4"/>
       <c r="K63" s="2"/>
     </row>
@@ -2943,19 +2969,15 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삽</t>
-        </is>
-      </c>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I64" s="2"/>
       <c r="J64" s="4"/>
       <c r="K64" s="2"/>
     </row>
@@ -2982,17 +3004,17 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사</t>
+          <t xml:space="preserve">곰</t>
         </is>
       </c>
       <c r="J65" s="4"/>
@@ -3021,19 +3043,15 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">히</t>
-        </is>
-      </c>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I66" s="2"/>
       <c r="J66" s="4"/>
       <c r="K66" s="2"/>
     </row>
@@ -3068,7 +3086,11 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="I67" s="2"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">히</t>
+        </is>
+      </c>
       <c r="J67" s="4"/>
       <c r="K67" s="2"/>
     </row>
@@ -3095,17 +3117,17 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가</t>
+          <t xml:space="preserve">생</t>
         </is>
       </c>
       <c r="J68" s="4"/>
@@ -3134,15 +3156,19 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I69" s="2"/>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">각</t>
+        </is>
+      </c>
       <c r="J69" s="4"/>
       <c r="K69" s="2"/>
     </row>
@@ -3167,22 +3193,26 @@
       <c r="F70" s="2">
         <v>3</v>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㒇^</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㒇^</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="J70" s="4"/>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">亻無 위 작은 ∪ 모양 꾸밈을 ^ 로</t>
+        </is>
+      </c>
       <c r="K70" s="2"/>
     </row>
     <row r="71">
@@ -3208,15 +3238,19 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">㑲</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I71" s="2"/>
+          <t xml:space="preserve">㑲</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">니</t>
+        </is>
+      </c>
       <c r="J71" s="4"/>
       <c r="K71" s="2"/>
     </row>
@@ -3243,12 +3277,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I72" s="2"/>
@@ -3278,12 +3312,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I73" s="2"/>
@@ -3313,17 +3347,17 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">㑲</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">㑲</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">빛</t>
+          <t xml:space="preserve">세</t>
         </is>
       </c>
       <c r="J74" s="4"/>
@@ -3352,19 +3386,15 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="I75" s="2"/>
       <c r="J75" s="4"/>
       <c r="K75" s="2"/>
     </row>
@@ -3401,7 +3431,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">큰</t>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
       <c r="J76" s="4"/>
@@ -3430,17 +3460,17 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">쌩</t>
+          <t xml:space="preserve">만</t>
         </is>
       </c>
       <c r="J77" s="4"/>
@@ -3469,17 +3499,17 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">쌩</t>
+          <t xml:space="preserve">사</t>
         </is>
       </c>
       <c r="J78" s="4"/>
@@ -3508,15 +3538,19 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I79" s="2"/>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
       <c r="J79" s="4"/>
       <c r="K79" s="2"/>
     </row>
@@ -3543,17 +3577,17 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">큰</t>
+          <t xml:space="preserve">춘</t>
         </is>
       </c>
       <c r="J80" s="4"/>
@@ -3582,19 +3616,16 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">–|無南</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+無南</t>
+        </is>
+      </c>
+      <c r="I81" s="2"/>
       <c r="J81" s="4"/>
       <c r="K81" s="2"/>
     </row>
@@ -3621,15 +3652,20 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">仲|姑</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I82" s="2"/>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">몽</t>
+        </is>
+      </c>
       <c r="J82" s="4"/>
       <c r="K82" s="2"/>
     </row>
@@ -3664,7 +3700,11 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="I83" s="2"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
       <c r="J83" s="4"/>
       <c r="K83" s="2"/>
     </row>
@@ -3691,12 +3731,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I84" s="2"/>
@@ -3726,15 +3766,19 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I85" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
       <c r="J85" s="4"/>
       <c r="K85" s="2"/>
     </row>
@@ -3761,15 +3805,19 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I86" s="2"/>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">또</t>
+        </is>
+      </c>
       <c r="J86" s="4"/>
       <c r="K86" s="2"/>
     </row>
@@ -3796,15 +3844,19 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I87" s="2"/>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="J87" s="4"/>
       <c r="K87" s="2"/>
     </row>
@@ -3829,27 +3881,22 @@
       <c r="F88" s="2">
         <v>1</v>
       </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無|僙</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-僙</t>
-        </is>
-      </c>
-      <c r="I88" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">각</t>
-        </is>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">무 아래 僙 겹침</t>
-        </is>
-      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시</t>
+        </is>
+      </c>
+      <c r="J88" s="4"/>
       <c r="K88" s="2"/>
     </row>
     <row r="89">
@@ -3873,27 +3920,22 @@
       <c r="F89" s="2">
         <v>2</v>
       </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲|僙</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲 아래 僙 겹침</t>
-        </is>
-      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈</t>
+        </is>
+      </c>
+      <c r="J89" s="4"/>
       <c r="K89" s="2"/>
     </row>
     <row r="90">
@@ -3919,12 +3961,12 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">㑲</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">㑲</t>
         </is>
       </c>
       <c r="I90" s="2"/>
@@ -3954,15 +3996,19 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I91" s="2"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">같</t>
+        </is>
+      </c>
       <c r="J91" s="4"/>
       <c r="K91" s="2"/>
     </row>
@@ -3989,15 +4035,19 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I92" s="2"/>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="J92" s="4"/>
       <c r="K92" s="2"/>
     </row>
@@ -4024,19 +4074,15 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I93" s="2"/>
       <c r="J93" s="4"/>
       <c r="K93" s="2"/>
     </row>
@@ -4063,19 +4109,15 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">니</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I94" s="2"/>
       <c r="J94" s="4"/>
       <c r="K94" s="2"/>
     </row>
@@ -4102,12 +4144,12 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I95" s="2"/>
@@ -4137,12 +4179,12 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I96" s="2"/>
@@ -4172,12 +4214,13 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I97" s="2"/>
@@ -4214,7 +4257,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4237,313 +4280,303 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="55.19" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C3" s="29"/>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">또</t>
+        </is>
+      </c>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">빛</t>
+          <t xml:space="preserve">㑲</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
         </is>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="G3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">빛</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">늘</t>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">곰</t>
+        </is>
+      </c>
+      <c r="H3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">푸</t>
         </is>
       </c>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="K3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">희</t>
         </is>
       </c>
       <c r="L3" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">㑲</t>
+        </is>
+      </c>
+      <c r="M3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">부</t>
+        </is>
+      </c>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">부</t>
-        </is>
-      </c>
-      <c r="N3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="O3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비</t>
-        </is>
-      </c>
-      <c r="P3" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="Q3" s="30" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">너</t>
+        </is>
+      </c>
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㑲</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="55.19" customHeight="1">
+    <row r="4" ht="52.21" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="G4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
-        </is>
-      </c>
+      <c r="G4" s="25"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">할</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I4" s="25"/>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="K4" s="31" t="inlineStr">
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">망</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">귀</t>
+        </is>
+      </c>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O4" s="25"/>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="Q4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">풍</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52.21" customHeight="1">
+      <c r="A5" s="0"/>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">시</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">상</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G5" s="26"/>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">른</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="K5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="M5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">와</t>
+        </is>
+      </c>
+      <c r="N5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">의</t>
+        </is>
+      </c>
+      <c r="P5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="Q5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">진</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52.21" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">꿈</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">만</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">곰</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^</t>
+        </is>
+      </c>
+      <c r="I6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">족</t>
         </is>
       </c>
-      <c r="L4" s="23" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">영</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M4" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">와</t>
-        </is>
-      </c>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="O4" s="31"/>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="Q4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">풍</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
-      <c r="A5" s="0"/>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-僙</t>
-        </is>
-      </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">각</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E5" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">큰</t>
-        </is>
-      </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="G5" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삽</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I5" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">삽</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="K5" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">영</t>
-        </is>
-      </c>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="M5" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">영</t>
-        </is>
-      </c>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O5" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">의</t>
-        </is>
-      </c>
-      <c r="P5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="Q5" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">진</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲
-僙</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">쌩</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="G6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">들</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="K6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화</t>
-        </is>
-      </c>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="M6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">화</t>
-        </is>
-      </c>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="O6" s="29" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">희</t>
         </is>
@@ -4553,68 +4586,68 @@
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="Q6" s="29" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="55.19" customHeight="1">
+    <row r="7" ht="52.21" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C7" s="31"/>
+          <t xml:space="preserve">㑲</t>
+        </is>
+      </c>
+      <c r="C7" s="25"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">쌩</t>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">히</t>
-        </is>
-      </c>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G7" s="25"/>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I7" s="31"/>
-      <c r="J7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K7" s="31"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I7" s="25"/>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㑲</t>
+        </is>
+      </c>
+      <c r="K7" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">족</t>
+        </is>
+      </c>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="M7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">를</t>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">화</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="O7" s="31" t="inlineStr">
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">망</t>
         </is>
@@ -4624,444 +4657,512 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q7" s="31" t="inlineStr">
+      <c r="Q7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">상</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="55.19" customHeight="1">
+    <row r="8" ht="52.21" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C8" s="34"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">같</t>
+        </is>
+      </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E8" s="34"/>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">히</t>
+        </is>
+      </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I8" s="34" t="inlineStr">
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">늘</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">할</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">를</t>
+        </is>
+      </c>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="O8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K8" s="34"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M8" s="34"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="O8" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
-        </is>
-      </c>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q8" s="34" t="inlineStr">
+      <c r="Q8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="55.19" customHeight="1">
+    <row r="9" ht="52.21" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="C9" s="29"/>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">큰</t>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">춘</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">생</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I9" s="29"/>
+          <t xml:space="preserve">汰</t>
+        </is>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">밝</t>
+        </is>
+      </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="K9" s="29" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">까</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">누</t>
         </is>
       </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="M9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">겨</t>
-        </is>
-      </c>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="O9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">구</t>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무</t>
         </is>
       </c>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="Q9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">무</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="Q9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">만</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52.21" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C10" s="25"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="E10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+無南</t>
+        </is>
+      </c>
+      <c r="E10" s="25"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="G10" s="31"/>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">각</t>
+        </is>
+      </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I10" s="31"/>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I10" s="25"/>
       <c r="J10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="K10" s="31"/>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K10" s="25"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M10" s="31"/>
+          <t xml:space="preserve">–
+無南</t>
+        </is>
+      </c>
+      <c r="M10" s="25"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="O10" s="31"/>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="O10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">엇</t>
+        </is>
+      </c>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="Q10" s="31"/>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
+          <t xml:space="preserve">–
+無南</t>
+        </is>
+      </c>
+      <c r="Q10" s="25"/>
+    </row>
+    <row r="11" ht="52.21" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C11" s="26"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">몽</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㒇^</t>
+        </is>
+      </c>
+      <c r="G11" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">니</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E11" s="34"/>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="G11" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="I11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">은</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I11" s="34"/>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="K11" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
+      <c r="K11" s="28"/>
       <c r="L11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M11" s="34"/>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="O11" s="34"/>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="M11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">렸</t>
+        </is>
+      </c>
+      <c r="N11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㒇^</t>
+        </is>
+      </c>
+      <c r="O11" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이</t>
+        </is>
+      </c>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="Q11" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">의</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="Q11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">났</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52.21" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="C12" s="29"/>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="E12" s="29"/>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">중</t>
+        </is>
+      </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="G12" s="29"/>
+          <t xml:space="preserve">㑲</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">니</t>
+        </is>
+      </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="I12" s="29"/>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달</t>
+        </is>
+      </c>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="K12" s="29"/>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="M12" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="M12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="O12" s="29"/>
+          <t xml:space="preserve">㑲</t>
+        </is>
+      </c>
+      <c r="O12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">냐</t>
+        </is>
+      </c>
       <c r="P12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="Q12" s="29"/>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
+      <c r="Q12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">으</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52.21" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="C13" s="31"/>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E13" s="31"/>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E13" s="25"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="G13" s="31"/>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G13" s="25"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="31"/>
-      <c r="J13" s="21" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="31"/>
-      <c r="L13" s="21" t="inlineStr">
+      <c r="M13" s="25"/>
+      <c r="N13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M13" s="31"/>
-      <c r="N13" s="21" t="inlineStr">
+      <c r="O13" s="27"/>
+      <c r="P13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="O13" s="31"/>
-      <c r="P13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q13" s="31"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
+      <c r="Q13" s="25"/>
+    </row>
+    <row r="14" ht="52.21" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="C14" s="34"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="C14" s="26"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="E14" s="34"/>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="G14" s="34"/>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G14" s="26"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">南</t>
+        </is>
+      </c>
+      <c r="I14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">래</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="K14" s="26"/>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="M14" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">면</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="34"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="K14" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">니</t>
-        </is>
-      </c>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="M14" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">영</t>
-        </is>
-      </c>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">僙</t>
-        </is>
-      </c>
-      <c r="O14" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">뭉</t>
-        </is>
-      </c>
+      <c r="O14" s="26"/>
       <c r="P14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="Q14" s="34" t="inlineStr">
+      <c r="Q14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>

--- a/sheets/민요/검수/희망가.xlsx
+++ b/sheets/민요/검수/희망가.xlsx
@@ -460,10 +460,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/희망가.xlsx
+++ b/sheets/민요/검수/희망가.xlsx
@@ -406,17 +406,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -533,7 +533,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -591,6 +591,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3983,590 +4027,590 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:Q14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B3" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="19" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B4" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7" t="s">
+      <c r="D4" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="22"/>
+      <c r="F4" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G4" s="22"/>
+      <c r="H4" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" s="22"/>
+      <c r="J4" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4" s="11" t="s">
+      <c r="L4" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="N4" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="O4" s="11"/>
-      <c r="P4" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q4" s="11" t="s">
+      <c r="N4" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="O4" s="22"/>
+      <c r="P4" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q4" s="22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B5" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="12" t="s">
+      <c r="D5" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="7" t="s">
+      <c r="G5" s="23"/>
+      <c r="H5" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="M5" s="12" t="s">
+      <c r="L5" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="O5" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="P5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q5" s="12" t="s">
+      <c r="P5" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q5" s="23" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B6" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="8" t="s">
+      <c r="L6" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="P6" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q6" s="8" t="s">
+      <c r="P6" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q6" s="19" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B7" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="7" t="s">
+      <c r="C7" s="22"/>
+      <c r="D7" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="G7" s="11"/>
-      <c r="H7" s="7" t="s">
+      <c r="G7" s="22"/>
+      <c r="H7" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="9" t="s">
+      <c r="I7" s="22"/>
+      <c r="J7" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="P7" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="Q7" s="11" t="s">
+      <c r="Q7" s="22" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B8" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="12" t="s">
+      <c r="F8" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="N8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="O8" s="12" t="s">
+      <c r="N8" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="O8" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="Q8" s="12" t="s">
+      <c r="Q8" s="23" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="8" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B9" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="J9" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="8" t="s">
+      <c r="J9" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="M9" s="8" t="s">
+      <c r="M9" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="P9" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="19" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B10" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="11" t="s">
+      <c r="E10" s="22"/>
+      <c r="F10" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="H10" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="7" t="s">
+      <c r="H10" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" s="22"/>
+      <c r="J10" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K10" s="22"/>
+      <c r="L10" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="11"/>
-      <c r="N10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="O10" s="11" t="s">
+      <c r="M10" s="22"/>
+      <c r="N10" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="O10" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="P10" s="7" t="s">
+      <c r="P10" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="Q10" s="11"/>
-    </row>
-    <row r="11" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="7" t="s">
+      <c r="Q10" s="22"/>
+    </row>
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B11" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="23"/>
+      <c r="D11" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="I11" s="12" t="s">
+      <c r="I11" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="J11" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="K11" s="14"/>
-      <c r="L11" s="7" t="s">
+      <c r="J11" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="K11" s="25"/>
+      <c r="L11" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="M11" s="12" t="s">
+      <c r="M11" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="N11" s="9" t="s">
+      <c r="N11" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="O11" s="14" t="s">
+      <c r="O11" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="P11" s="7" t="s">
+      <c r="P11" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="Q11" s="12" t="s">
+      <c r="Q11" s="23" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="8" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B12" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="M12" s="8" t="s">
+      <c r="J12" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="19"/>
+      <c r="L12" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="M12" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O12" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="P12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q12" s="8" t="s">
+      <c r="P12" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q12" s="19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="7" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B13" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="22"/>
+      <c r="F13" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" s="22"/>
+      <c r="H13" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="J13" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="M13" s="11"/>
-      <c r="N13" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="O13" s="13"/>
-      <c r="P13" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q13" s="11"/>
-    </row>
-    <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="J13" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="K13" s="22"/>
+      <c r="L13" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="M13" s="22"/>
+      <c r="N13" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="O13" s="24"/>
+      <c r="P13" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q13" s="22"/>
+    </row>
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+      <c r="B14" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="12"/>
-      <c r="D14" s="7" t="s">
+      <c r="C14" s="23"/>
+      <c r="D14" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="F14" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="7" t="s">
+      <c r="F14" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="23"/>
+      <c r="H14" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I14" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="K14" s="12"/>
-      <c r="L14" s="7" t="s">
+      <c r="K14" s="23"/>
+      <c r="L14" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="M14" s="12" t="s">
+      <c r="M14" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="N14" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="O14" s="12"/>
-      <c r="P14" s="7" t="s">
+      <c r="N14" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="O14" s="23"/>
+      <c r="P14" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="Q14" s="12" t="s">
+      <c r="Q14" s="23" t="s">
         <v>64</v>
       </c>
     </row>
@@ -4576,7 +4620,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="76" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/희망가.xlsx
+++ b/sheets/민요/검수/희망가.xlsx
@@ -4033,26 +4033,26 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.52" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -4072,7 +4072,7 @@
       <c r="P2" s="17"/>
       <c r="Q2" s="17"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>53</v>
       </c>
@@ -4122,7 +4122,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B4" s="18" t="s">
         <v>53</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>53</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B6" s="18" t="s">
         <v>52</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B7" s="18" t="s">
         <v>46</v>
       </c>
@@ -4306,7 +4306,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B8" s="18" t="s">
         <v>52</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B9" s="18" t="s">
         <v>48</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B10" s="18" t="s">
         <v>74</v>
       </c>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="Q10" s="22"/>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B11" s="18" t="s">
         <v>74</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B12" s="18" t="s">
         <v>74</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B13" s="18" t="s">
         <v>74</v>
       </c>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="Q13" s="22"/>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="102.71" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="96.05" customHeight="true">
       <c r="B14" s="18" t="s">
         <v>90</v>
       </c>
@@ -4620,7 +4620,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
